--- a/data/odds/AGP 30 2026 Betting Odds.xlsx
+++ b/data/odds/AGP 30 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
   <si>
     <t>Record</t>
   </si>
@@ -36,187 +36,202 @@
     <t>Jimmys</t>
   </si>
   <si>
+    <t>Chiefs Nation</t>
+  </si>
+  <si>
     <t>Gage's Grand Team</t>
   </si>
   <si>
     <t>Q</t>
   </si>
   <si>
-    <t>Chiefs Nation</t>
+    <t>Them Boys</t>
   </si>
   <si>
     <t>max's Monstrous Team</t>
   </si>
   <si>
+    <t>Shake N' Bake</t>
+  </si>
+  <si>
     <t>Milk Man</t>
   </si>
   <si>
-    <t>Them Boys</t>
-  </si>
-  <si>
-    <t>Shake N' Bake</t>
-  </si>
-  <si>
     <t>Pats4life</t>
   </si>
   <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>99.3%</t>
-  </si>
-  <si>
-    <t>98.3%</t>
-  </si>
-  <si>
-    <t>95.5%</t>
-  </si>
-  <si>
-    <t>79.4%</t>
-  </si>
-  <si>
-    <t>75.7%</t>
-  </si>
-  <si>
-    <t>68.9%</t>
-  </si>
-  <si>
-    <t>32.4%</t>
-  </si>
-  <si>
-    <t>28.2%</t>
-  </si>
-  <si>
-    <t>19.4%</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>96.7%</t>
+  </si>
+  <si>
+    <t>89.5%</t>
+  </si>
+  <si>
+    <t>79.1%</t>
+  </si>
+  <si>
+    <t>72.2%</t>
+  </si>
+  <si>
+    <t>56.7%</t>
+  </si>
+  <si>
+    <t>47.4%</t>
+  </si>
+  <si>
+    <t>35.8%</t>
+  </si>
+  <si>
+    <t>11.9%</t>
+  </si>
+  <si>
+    <t>10.9%</t>
+  </si>
+  <si>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-2930</t>
+  </si>
+  <si>
+    <t>-852</t>
+  </si>
+  <si>
+    <t>-378</t>
+  </si>
+  <si>
+    <t>-260</t>
+  </si>
+  <si>
+    <t>-131</t>
+  </si>
+  <si>
+    <t>+111</t>
+  </si>
+  <si>
+    <t>+179</t>
+  </si>
+  <si>
+    <t>+740</t>
+  </si>
+  <si>
+    <t>+817</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>75.2%</t>
+  </si>
+  <si>
+    <t>13.9%</t>
+  </si>
+  <si>
+    <t>6.0%</t>
   </si>
   <si>
     <t>2.9%</t>
   </si>
   <si>
-    <t>-14186</t>
-  </si>
-  <si>
-    <t>-5782</t>
-  </si>
-  <si>
-    <t>-2122</t>
-  </si>
-  <si>
-    <t>-385</t>
-  </si>
-  <si>
-    <t>-312</t>
-  </si>
-  <si>
-    <t>-222</t>
-  </si>
-  <si>
-    <t>+209</t>
-  </si>
-  <si>
-    <t>+255</t>
-  </si>
-  <si>
-    <t>+415</t>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-303</t>
+  </si>
+  <si>
+    <t>+619</t>
+  </si>
+  <si>
+    <t>+1567</t>
   </si>
   <si>
     <t>+3348</t>
   </si>
   <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>50.6%</t>
-  </si>
-  <si>
-    <t>27.7%</t>
-  </si>
-  <si>
-    <t>14.7%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
-  </si>
-  <si>
-    <t>2.2%</t>
+    <t>+14186</t>
+  </si>
+  <si>
+    <t>+19900</t>
+  </si>
+  <si>
+    <t>+24900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>39.8%</t>
+  </si>
+  <si>
+    <t>34.1%</t>
+  </si>
+  <si>
+    <t>11.5%</t>
+  </si>
+  <si>
+    <t>6.4%</t>
+  </si>
+  <si>
+    <t>4.7%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-102</t>
-  </si>
-  <si>
-    <t>+261</t>
-  </si>
-  <si>
-    <t>+580</t>
-  </si>
-  <si>
-    <t>+4248</t>
-  </si>
-  <si>
-    <t>+4445</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>60.0%</t>
-  </si>
-  <si>
-    <t>17.4%</t>
-  </si>
-  <si>
-    <t>10.9%</t>
-  </si>
-  <si>
-    <t>8.4%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>-150</t>
-  </si>
-  <si>
-    <t>+475</t>
-  </si>
-  <si>
-    <t>+817</t>
-  </si>
-  <si>
-    <t>+1090</t>
+    <t>+151</t>
+  </si>
+  <si>
+    <t>+193</t>
+  </si>
+  <si>
+    <t>+770</t>
+  </si>
+  <si>
+    <t>+1462</t>
+  </si>
+  <si>
+    <t>+2028</t>
   </si>
   <si>
     <t>+5782</t>
   </si>
   <si>
-    <t>+11011</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>+6567</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -599,10 +614,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -610,13 +625,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -624,13 +639,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -641,10 +656,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -655,10 +670,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -666,13 +681,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -680,13 +695,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -694,13 +709,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -708,13 +723,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -722,13 +737,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -749,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -763,7 +778,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>47</v>
@@ -774,10 +789,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>48</v>
@@ -788,10 +803,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>49</v>
@@ -799,13 +814,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
         <v>50</v>
@@ -819,7 +834,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -827,7 +842,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -836,63 +851,63 @@
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -913,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -924,13 +939,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -938,13 +953,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -952,13 +967,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -966,13 +981,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -980,13 +995,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -997,10 +1012,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1011,52 +1026,52 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/AGP 30 2026 Betting Odds.xlsx
+++ b/data/odds/AGP 30 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
   <si>
     <t>Record</t>
   </si>
@@ -75,106 +75,103 @@
     <t>99.8%</t>
   </si>
   <si>
-    <t>96.7%</t>
-  </si>
-  <si>
-    <t>89.5%</t>
-  </si>
-  <si>
-    <t>79.1%</t>
-  </si>
-  <si>
-    <t>72.2%</t>
-  </si>
-  <si>
-    <t>56.7%</t>
-  </si>
-  <si>
-    <t>47.4%</t>
-  </si>
-  <si>
-    <t>35.8%</t>
-  </si>
-  <si>
-    <t>11.9%</t>
-  </si>
-  <si>
-    <t>10.9%</t>
+    <t>95.7%</t>
+  </si>
+  <si>
+    <t>89.0%</t>
+  </si>
+  <si>
+    <t>78.1%</t>
+  </si>
+  <si>
+    <t>71.2%</t>
+  </si>
+  <si>
+    <t>59.4%</t>
+  </si>
+  <si>
+    <t>49.8%</t>
+  </si>
+  <si>
+    <t>37.8%</t>
+  </si>
+  <si>
+    <t>11.4%</t>
+  </si>
+  <si>
+    <t>7.8%</t>
   </si>
   <si>
     <t>-49900</t>
   </si>
   <si>
-    <t>-2930</t>
-  </si>
-  <si>
-    <t>-852</t>
-  </si>
-  <si>
-    <t>-378</t>
-  </si>
-  <si>
-    <t>-260</t>
-  </si>
-  <si>
-    <t>-131</t>
-  </si>
-  <si>
-    <t>+111</t>
-  </si>
-  <si>
-    <t>+179</t>
-  </si>
-  <si>
-    <t>+740</t>
-  </si>
-  <si>
-    <t>+817</t>
+    <t>-2226</t>
+  </si>
+  <si>
+    <t>-809</t>
+  </si>
+  <si>
+    <t>-357</t>
+  </si>
+  <si>
+    <t>-247</t>
+  </si>
+  <si>
+    <t>-146</t>
+  </si>
+  <si>
+    <t>+101</t>
+  </si>
+  <si>
+    <t>+165</t>
+  </si>
+  <si>
+    <t>+777</t>
+  </si>
+  <si>
+    <t>+1182</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>75.2%</t>
-  </si>
-  <si>
-    <t>13.9%</t>
-  </si>
-  <si>
-    <t>6.0%</t>
-  </si>
-  <si>
-    <t>2.9%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
+    <t>74.0%</t>
+  </si>
+  <si>
+    <t>15.0%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>2.5%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
+    <t>0.1%</t>
+  </si>
+  <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-303</t>
-  </si>
-  <si>
-    <t>+619</t>
-  </si>
-  <si>
-    <t>+1567</t>
-  </si>
-  <si>
-    <t>+3348</t>
-  </si>
-  <si>
-    <t>+14186</t>
-  </si>
-  <si>
-    <t>+19900</t>
+    <t>-285</t>
+  </si>
+  <si>
+    <t>+567</t>
+  </si>
+  <si>
+    <t>+1438</t>
+  </si>
+  <si>
+    <t>+3900</t>
+  </si>
+  <si>
+    <t>+8991</t>
   </si>
   <si>
     <t>+24900</t>
@@ -183,22 +180,22 @@
     <t>+99900</t>
   </si>
   <si>
-    <t>39.8%</t>
-  </si>
-  <si>
-    <t>34.1%</t>
-  </si>
-  <si>
-    <t>11.5%</t>
-  </si>
-  <si>
-    <t>6.4%</t>
-  </si>
-  <si>
-    <t>4.7%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
+    <t>41.9%</t>
+  </si>
+  <si>
+    <t>35.4%</t>
+  </si>
+  <si>
+    <t>9.7%</t>
+  </si>
+  <si>
+    <t>5.4%</t>
+  </si>
+  <si>
+    <t>3.6%</t>
+  </si>
+  <si>
+    <t>2.3%</t>
   </si>
   <si>
     <t>1.5%</t>
@@ -207,25 +204,22 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>+151</t>
-  </si>
-  <si>
-    <t>+193</t>
-  </si>
-  <si>
-    <t>+770</t>
-  </si>
-  <si>
-    <t>+1462</t>
-  </si>
-  <si>
-    <t>+2028</t>
-  </si>
-  <si>
-    <t>+5782</t>
+    <t>+139</t>
+  </si>
+  <si>
+    <t>+182</t>
+  </si>
+  <si>
+    <t>+931</t>
+  </si>
+  <si>
+    <t>+1752</t>
+  </si>
+  <si>
+    <t>+2678</t>
+  </si>
+  <si>
+    <t>+4248</t>
   </si>
   <si>
     <t>+6567</t>
@@ -842,10 +836,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
@@ -856,24 +850,24 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>45</v>
@@ -893,7 +887,7 @@
         <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -907,7 +901,7 @@
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -942,10 +936,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -956,10 +950,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -970,10 +964,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -984,10 +978,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -998,10 +992,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1012,10 +1006,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1026,43 +1020,43 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1071,7 +1065,7 @@
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
